--- a/tests/fixtures/pilot/1clinical_goals_90000001_Auto.xlsx
+++ b/tests/fixtures/pilot/1clinical_goals_90000001_Auto.xlsx
@@ -569,7 +569,7 @@
         <v>4500</v>
       </c>
       <c r="G4" t="n">
-        <v>95</v>
+        <v>0.95</v>
       </c>
       <c r="H4" t="n">
         <v>4550.2</v>
